--- a/Project_Up/dailyTop.xlsx
+++ b/Project_Up/dailyTop.xlsx
@@ -10,6 +10,17 @@
     <sheet name="2026-09-04" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-09-07" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-09-08" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-09-10" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-09-11" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-09-14" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-09-15" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-09-16" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-09-17" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-09-18" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-09-21" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-09-22" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-09-23" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-09-24" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -777,6 +788,1656 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ISFT</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ALKALI</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>21.36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MANUGRAPH</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>20.34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SHIVAMAUTO</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>18.92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>NGIL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16.57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TIMEX</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>15.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>RUSHIL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>14.22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CUBEXTUB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>13.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SAMBHV</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>13.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SURAJEST</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>13.13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>VISAKAIND</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>11.91</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>KNAGRI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MACPOWER</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>11.48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LUXIND</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>NRBBEARING</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MBECL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>UNIVASTU</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BGRENERGY</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>BODALCHEM</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SALSTEEL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>GFSTEELS</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>KAYA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SOFTTECH</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CAPTRUST</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BHAGERIA</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>JETFREIGHT</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>9.859999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PROTEAN</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SRHHYPOLTD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ARVEE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>INDORAMA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>16.19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CROWN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SURAJEST</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>KPIGREEN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12.92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>RATNAVEER</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>JAYKAY</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ASHIANA</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>11.35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ZOTA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11.18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ALKALI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>10.79</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>JASH</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TARSONS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>10.41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SILVERTUC</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AHCL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TEGA</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>DEVX</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RSL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ORCHPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ISGEC</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SHADOWFAX</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>FILATEX</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BALPHARMA</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CPCAP</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>BHAGERIA</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>8.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>OPTIEMUS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CRESTO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>CUBEXTUB</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>REGAAL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>15.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TRANSRAILL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ARVEE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>12.76</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TCC</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ASTEC</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ISFT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>STEELCAS</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SSDL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GANDHITUBE</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>10.13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PACEDIGITK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>AHCL</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>NIBL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>9.470000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MEESHO</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SHIVAUM</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CHEMPLASTS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>8.970000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ITDC</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>UNIECOM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>8.369999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MANUGRAPH</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BLUESTONE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>AVTNPL</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GTECJAINX</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>SGIL</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ARIHANTCAP</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>OPTIEMUS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>39.81</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>23.52</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PREMIERPOL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>20.63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CUBEXTUB</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SRGHFL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>19.32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MANUGRAPH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>17.66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>EKC</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>15.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ISFT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ARIHANTCAP</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MUKANDLTD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>LOYALTEX</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>14.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ATLASCYCLE</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>14.17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>REGAAL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>13.22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>RAYMONDREL</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>13.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SHANTIGOLD</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SGIL</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>12.47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MANINDS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>AHCL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>11.93</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>JAYKAY</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ELECON</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>AARTIPHARM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>11.29</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>DELTACORP</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>KOTHARIPRO</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>10.36</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RPTECH</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>KILITCH</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>AERONEU</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>CRESTO</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.96</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RKEC</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>INDIAGLYCO</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LAMBODHARA</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>17.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DCI</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>UNIDT</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>REMSONSIND</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MITCON</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>KABRAEXTRU</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CUBEXTUB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>KSCL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GLOTTIS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>VIKRAN</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SEDEMAC</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8.18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>JAGSNPHARM</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>GREAVESCOT</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PRAENG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>JAMNAAUTO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>BOHRAIND</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ABDL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>AVANTEL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BLUSPRING</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>CRIZAC</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HGINFRA</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>WEWIN</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ADL</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1435,4 +3096,1984 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SSDL</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>DIGJAMLMTD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.98</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KAVDEFENCE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BIOFILCHEM</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>16.94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>OSWALSEEDS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>12.77</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ANMOL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>NOVARTIND</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>MANINDS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>INDOCO</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>LGHL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MANGALAM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MERCURYEV</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ZFSTEERING</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GENESYS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>STEELCITY</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8.720000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>VSSL</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AHCL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>AGROPHOS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SHAKTIPUMP</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SAYAJIHOTL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SWANCORP</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SREEL</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MAHAPEXLTD</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>LIBAS</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>KABRAEXTRU</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>STARPAPER</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ANDHRAPAP</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>JUNIPER</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SIGACHI</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>MANAKSIA</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ASHOKAMET</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>19.94</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>16.84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>AWFIS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>16.83</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>VGL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>14.69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>FILATEX</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DIGJAMLMTD</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SMSPHARMA</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AHCL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TRACXN</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HLEGLAS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MONEYBOXX</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ANMOL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9.970000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NIBL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>INCREDIBLE</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>AMDIND</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RACLGEAR</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>9.48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>QUADFUTURE</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>UGARSUGAR</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ELANTAS</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PRIMO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>AIIL</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MOBIKWIK</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>BBOX</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>KIRLOSIND</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7.08</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BLACKBUCK</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7.07</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>FINKURVE</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TEXMOPIPES</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ORIENTTECH</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ASHOKAMET</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>19.94</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>AWFIS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>17.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>17.44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>VGL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>15.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>FILATEX</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>14.64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AMDIND</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>AHCL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>11.57</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TRACXN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SMSPHARMA</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>11.02</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>DIGJAMLMTD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RACLGEAR</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HLEGLAS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MONEYBOXX</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ANMOL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.970000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>QUADFUTURE</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PRIMO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>NAGREEKCAP</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8.880000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>UGARSUGAR</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>NIBL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8.67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FINKURVE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>INCREDIBLE</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ELANTAS</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MOBIKWIK</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BBOX</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BLACKBUCK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>KIRLOSIND</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>7.03</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TEXMOPIPES</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>AIIL</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HMAAGRO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>18.98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>KAVDEFENCE</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>13.44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>RELCHEMQ</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TATAINVEST</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>AMDIND</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>NAGREEKCAP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MONEYBOXX</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GTECJAINX</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>IGARASHI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>JINDALPOLY</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SHOPERSTOP</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>JINDALPHOT</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>KOPRAN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6.78</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>QUICKHEAL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>OPTIEMUS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SONATSOFTW</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>VMSTMT</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GEEKAYWIRE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ONMOBILE</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>KANORICHEM</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>MBECL</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>KESORAMIND</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>UNIVPHOTO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>12.02</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>NPST</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>FOSECOIND</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MONEYBOXX</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>INDTERRAIN</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>9.960000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ISHANCH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ARROWGREEN</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>9.460000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ATAM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SHIVALIK</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>8.970000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CSBBANK</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>8.470000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MOREPENLAB</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RUBYMILLS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>7.79</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KRYSTAL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>7.79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>IOLCP</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>KARMAENG</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MATRIMONY</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MEDICAMEQ</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SHRADHA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MOTISONS</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>VMSTMT</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SAATVIKGL</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TATVA</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>HLEGLAS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SALZERELEC</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>LOKESHMACH</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SBGLP</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20.86</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ISFT</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>17.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MONEYBOXX</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>RMC</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>13.51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TREL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>12.72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TEGA</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ISHANCH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11.34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>HALDER</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ATAM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ASTEC</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10.79</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MVGJL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MBECL</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BHAGYANGR</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>BURNPUR</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GFSTEELS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BGRENERGY</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AHLWEST</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ATALREAL</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>9.970000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SALSTEEL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>AHLADA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SHAREINDIA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>KARMAENG</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>9.119999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>UNIVPHOTO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>YATHARTH</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>MATRIMONY</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CSBBANK</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>8.109999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Project_Up/dailyTop.xlsx
+++ b/Project_Up/dailyTop.xlsx
@@ -21,6 +21,19 @@
     <sheet name="2026-09-22" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="2026-09-23" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="2026-09-24" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-09-28" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-09-29" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-09-30" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-10-01" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-10-05" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-10-06" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-10-07" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-10-08" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-10-09" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-10-12" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-10-13" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-10-15" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-10-16" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -794,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -816,237 +829,237 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ISFT</t>
+          <t>SHIVAMAUTO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>25.99</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>GRAUWEIL</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>21.36</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>NGIL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>20.34</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SHIVAMAUTO</t>
+          <t>TIMEX</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>18.92</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GRAUWEIL</t>
+          <t>RUSHIL</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>17.48</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NGIL</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>16.57</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TIMEX</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>15.47</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>RUSHIL</t>
+          <t>SURAJEST</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>14.22</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>13.21</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SAMBHV</t>
+          <t>VISAKAIND</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>13.16</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SURAJEST</t>
+          <t>KNAGRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>13.13</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>13.04</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>11.91</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>11.51</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11.48</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>11.37</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>UNIVASTU</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>11.2</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>BGRENERGY</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10.94</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>UNIVASTU</t>
+          <t>SALSTEEL</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BGRENERGY</t>
+          <t>GFSTEELS</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10.25</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>KAYA</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SALSTEEL</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GFSTEELS</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1056,60 +1069,30 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KAYA</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>JETFREIGHT</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10.23</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10.23</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>BHAGERIA</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>10.22</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>JETFREIGHT</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>10.05</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>SHILPAMED</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
         <v>9.859999999999999</v>
       </c>
     </row>
@@ -1784,7 +1767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1806,300 +1789,270 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>39.81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>23.52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PREMIERPOL</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>20.63</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>WHIRLPOOL</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>EKC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>20</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>ISFT</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>19.32</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>17.66</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>EKC</t>
+          <t>MUKANDLTD</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>15.94</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ISFT</t>
+          <t>LOYALTEX</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>15.75</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>ATLASCYCLE</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>15.3</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>15.16</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>LOYALTEX</t>
+          <t>REGAAL</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>14.55</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ATLASCYCLE</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>14.17</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>SHANTIGOLD</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>13.42</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>13.22</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>MANINDS</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>13.06</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12.85</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>JAYKAY</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>12.47</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MANINDS</t>
+          <t>ELECON</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>12.2</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>11.93</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>JAYKAY</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>11.92</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ELECON</t>
+          <t>ADROITINFO</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11.33</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>11.31</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>11.29</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>KOTHARIPRO</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>11.01</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>RPTECH</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10.68</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10.59</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>KOTHARIPRO</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>10.36</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>RPTECH</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>10.32</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>KILITCH</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
         <v>10.25</v>
       </c>
     </row>
@@ -2438,6 +2391,1656 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STARTECK</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TNTELE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>REPRO</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>15.77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SMCGLOBAL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SSDL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RSYSTEMS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PRIMO</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SYNCOMF</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DAMCAPITAL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CUBEXTUB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>AHCL</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HINDCON</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ARVEE</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EUROTEXIND</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>PRITIKAUTO</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>8.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>AASTHA</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>DCI</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SDBL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MACPOWER</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>DIVGIITTS</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6.92</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OPTIEMUS</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>CRESTO</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>EMKAY</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SHIVAUM</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>INDOBORAX</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BOROLTD</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PFS</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>AEQUS</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DPABHUSHAN</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PASHUPATI</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>JHS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>19.98</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TNTELE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>19.93</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SYNCOMF</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>15.09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ORBTEXP</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>14.46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>11.48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TCIEXP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DGCONTENT</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10.36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AXISCADES</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>HINDCON</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GTECJAINX</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9.970000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>RAMBHAJO</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9.890000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KOTYARK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>RSYSTEMS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ESSARSHPNG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>INDOCO</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BOSCH-HCIL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>AZAD</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PGHL</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>JNKINDIA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>STARTECK</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BALPHARMA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>INDOAMIN</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>DOLLEX</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>WEALTH</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>OMNI</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.83</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>VIKRAN</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ALICON</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>JHS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.94</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ESTER</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>IRCON</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ARTNIRMAN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TVSELECT</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>11.81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>VALIANTORG</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ESSARSHPNG</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>11.56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>EUROTEXIND</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GTECJAINX</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.970000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TPLPLASTEH</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9.470000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NPST</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DPABHUSHAN</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>AXISCADES</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CUPID</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>8.140000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>EMIL</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GENCON</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>THELEELA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>HUBTOWN</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GREENPLY</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>KREBSBIO</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>IITL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>MUNJALAU</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ARIS</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>JWL</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>MOREPENLAB</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SMLT</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>XELPMOC</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>14.03</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RVTH</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>13.77</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>KREBSBIO</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>GKSL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LGHL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>EUROTEXIND</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GTECJAINX</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>VIVIANA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>LOKESHMACH</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8.76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MTNL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ATLANTAELE</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>OMNI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>NKIND</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PIXTRANS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MOREPENLAB</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>HILINFRA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>INOXINDIA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>DIFFNKG</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>STLTECH</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>INDOTECH</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>NINSYS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SIGMAADV</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>MODISONLTD</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>MMWL</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>RELINFRA</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DCMSHRIRAM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>DPWIRES</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KRISHNADEF</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SMCGLOBAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DELTACORP</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12.72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DPABHUSHAN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12.19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PREMIERPOL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ATLANTAELE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>AVADHSUGAR</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MANALIPETC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>LOKESHMACH</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SCI</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KRYSTAL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8.539999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BATLIBOI</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>JAYKAY</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>DALMIASUG</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>KILITCH</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>GEEKAYWIRE</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SGFIN</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MARINE</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HALDER</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TERASOFT</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>6.78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SMLT</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PALASHSECU</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>BLKASHYAP</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2768,7 +4371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2796,300 +4399,3447 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>33.23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>23.47</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PODDARMENT</t>
+          <t>AMNPLST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>22.71</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>18.46</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GENESYS</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>17.43</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BAIDFIN</t>
+          <t>DPWIRES</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>17.09</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>VENUSPIPES</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>16.68</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>15.96</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>15.62</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MVGJL</t>
+          <t>INDOAMIN</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>15.59</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>CEINSYS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>15.48</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>13.54</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>13.5</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>MIDWESTLTD</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>13.24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>12.67</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>KOTHARIPET</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>12.63</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>ELGIRUBCO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12.44</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>YUKEN</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>11.7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>FCL</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>11.53</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>VINDHYATEL</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>11.18</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>GYFTR</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10.94</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>WHEELS</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RISHABH</t>
+          <t>MANGALAM</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10.42</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>URBANCO</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>10.25</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>MAXIND</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>10.25</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SYSTMTXC</t>
+          <t>JGCHEM</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10.24</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10.24</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>10.22</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>10.22</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>GENUSPOWER</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>INDIAGLYCO</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>NELCAST</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>16.52</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CINEVISTA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>14.82</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MBEL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>14.71</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PNGSREVA</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DHANBANK</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11.76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>MARSONS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RUDRA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>GANESHCP</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RAJOOENG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>8.970000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>JAYKAY</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RAMBHAJO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CHEMPLASTS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>WALCHANNAG</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TFCILTD</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>EPACKPEB</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>OMPOWER</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>GPTINFRA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>KNACK</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SYNCOMF</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MIDWESTLTD</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PTCIL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6.83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ICEMAKE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>MEGASTAR</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>EBGNG</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>AVADHSUGAR</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>CINELINE</t>
+        </is>
+      </c>
       <c r="B31" s="3" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NELCAST</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>146.29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PNGSREVA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DHANBANK</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>32.83</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MBEL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>290.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FINOPB</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>145.53</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CINEVISTA</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>15.37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RAJOOENG</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>62.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>RUDRA</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>19.46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GANESHCP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>158.87</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TFCILTD</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>152.24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EPACKPEB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>267.44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1343.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IBULLSLTD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>34.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ARFIN</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>103.06</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GPTINFRA</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>130.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ICEMAKE</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>673.35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>XELPMOC</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>91.31999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>AGROPHOS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>23.38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BHARTIHEXA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1477.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CINELINE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>93.34999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>DEEPINDS</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>795.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ASTEC</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>748.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ORIENTTECH</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>239.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CELLO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>390.65</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ZIMLAB</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>146.61</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PCJEWELLER</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>WCIL</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>92.54000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CYIENTDLM</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>988.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>JAMNAAUTO</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>151.77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TARAPUR</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>16.58</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WORTHPERI</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>157.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TRF</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>219.69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>INOXGREEN</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>131.37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RSYSTEMS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>276.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>110.85</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SUNCLAY</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1220.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>WEALTH</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>927.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MODINATUR</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>318.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>BMWVENTLTD</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>54.77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>UEL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>214.94</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DHRUV</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>23.03</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>JKIPL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>113.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>AVTNPL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>93.44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AMNPLST</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>180.98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SHANTIGOLD</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>381.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PRAENG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SURAJLTD</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>200.47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PRUDMOULI</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>14.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>MMWL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SECMARK</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>150.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>GLOBALE</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PRIMO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>KEC</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>375.35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BSHSL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1160.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PCJEWELLER</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>14.87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>66.77</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>JPOLYINVST</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>938.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TCPLPACK</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>4270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WSTCSTPAPR</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>873.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SHRINGARMS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>265.35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CPCAP</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>175.66</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>GALLANTT</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>587.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MAWANASUG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>167.27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>184.49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GOODLUCK</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>567.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ADVANCE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>UTTAMSUGAR</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>336.45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ASIANTILES</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GRMOVER</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>89.84999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RAJSREESUG</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>30.71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>NRAIL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>AEROENTER</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>136.96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PREMIERPOL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>113.85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>IVP</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>242.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>IDEAFORGE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>735.45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>BTTL</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>42.26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MCLEODRUSS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>45.35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>DALMIASUG</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TARAPUR</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>18.23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>OMAXAUTO</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MMWL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>22.97</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>BMWVENTLTD</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>639.75</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SWARAJENG</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>3727.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>282.75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>CARTRADE</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>3191.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>408.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ONWARDTEC</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GUJRAFFIA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>52.11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WSI</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>64.45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MAWANASUG</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>175.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>911.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>NRAIL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>753.45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>190.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GALLANTT</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>587.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>MCLEODRUSS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>47.91</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PNCINFRA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>156.27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>WSTCSTPAPR</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>837.45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ASIANTILES</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>52.19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>VIKRAN</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>63.76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HATHWAY</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GRMOVER</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>90.73999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BMWVENTLTD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>65.55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>DALMIASUG</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>490.35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MAGADSUGAR</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>606.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>CPCAP</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>164.73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>LAMBODHARA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>144.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ARTNIRMAN</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>43.71</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MAZDA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>GOODLUCK</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RAJSREESUG</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>30.83</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SAGARDEEP</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BLKASHYAP</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>61.68</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>IDEAFORGE</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>745.55</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>705.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>128.41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>BIGBLOC</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>40.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MODINATUR</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>375.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SHREERAMA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>49.17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>OAL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>GALLANTT</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>WSI</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>71.98999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>BANKA</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BMWVENTLTD</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>XTGLOBAL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>27.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SEJALLTD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>953.95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>JAICORPLTD</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>93.63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ORIENTELEC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>188.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>JAIBALAJI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>75.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BUTTERFLY</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>614.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>JKIPL</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>127.47</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>VIRINCHI</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>UGROCAP</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>84.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GODAVARIB</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>246.01</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>BEDMUTHA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>116.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SHREYANIND</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>147.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ASHOKAMET</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1230.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TEAMLEASE</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1132.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RUBFILA</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>66.37</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>PASHUPATI</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>81.38</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ALLTIME</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>209.62</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>LINC</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>90.48999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ONWARDTEC</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>427.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SINGERIND</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>90.09</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>833.15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SHREERAMA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>58.53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>183.37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>OSWALAGRO</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>36.66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PCJEWELLER</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>IGCL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>61.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LEXUS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>STANLEY</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>VASCONEQ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>WORTHPERI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>168.89</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TOKYOPLAST</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>70.95999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MCLEODRUSS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>51.51</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KESORAMIND</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BCONCEPTS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>146.73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>746.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>OAL</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>629.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SHANTIGOLD</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>423.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PRAKASH</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>126.91</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>28.12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>22.51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>NGIL</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MVGJL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>225.27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SOLARA</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>696.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>DHANBANK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>35.79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BIGBLOC</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>43.24</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PARACABLES</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>60.52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SHRIPISTON</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>4629.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MMP</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>18.46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>GENESYS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>17.43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BAIDFIN</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>17.09</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>VENUSPIPES</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>16.68</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ASTEC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>15.96</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>15.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MVGJL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>15.59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>15.48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BODALCHEM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>13.54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MIDHANI</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>13.24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>CORDSCABLE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>KOTHARIPET</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>12.63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SAKAR</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CHEMBOND</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>AIRAN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>11.53</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RAYMONDREL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>11.18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>GMMPFAUDLR</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>WHEELS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RISHABH</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>MBECL</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SYSTMTXC</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>STLTECH</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>STLNETWORK</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BHAGERIA</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>INDIAGLYCO</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>10.22</v>
       </c>
     </row>
@@ -4754,7 +9504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4776,117 +9526,117 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SBGLP</t>
+          <t>ISFT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>20.86</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ISFT</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>17.85</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>RMC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>15.49</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>RMC</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13.51</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>12.72</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>11.9</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ISHANCH</t>
+          <t>HALDER</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11.34</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>HALDER</t>
+          <t>ATAM</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10.94</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ATAM</t>
+          <t>ASTEC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.82</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ASTEC</t>
+          <t>MVGJL</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10.79</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MVGJL</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10.48</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -4896,77 +9646,77 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BHAGYANGR</t>
+          <t>BURNPUR</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>BURNPUR</t>
+          <t>GFSTEELS</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GFSTEELS</t>
+          <t>BGRENERGY</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>10.19</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BGRENERGY</t>
+          <t>AHLWEST</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>10.08</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AHLWEST</t>
+          <t>ATALREAL</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ATALREAL</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>SALSTEEL</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>SALSTEEL</t>
+          <t>AHLADA</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -4976,100 +9726,90 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AHLADA</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>9.75</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>9.68</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>KARMAENG</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>KARMAENG</t>
+          <t>UNIVPHOTO</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>UNIVPHOTO</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8.6</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>MATRIMONY</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>8.57</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MATRIMONY</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>8.130000000000001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>SYRMA</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
         <v>8.109999999999999</v>
       </c>
     </row>
